--- a/ig/DM-FEVRIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-FEVRIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:51:23+00:00</t>
+    <t>2025-02-28T10:48:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-FEVRIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-FEVRIER-2025/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:48:02+00:00</t>
+    <t>2025-02-28T14:32:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
